--- a/Exponentia Yol Planı ve Gannt Chart.xlsx
+++ b/Exponentia Yol Planı ve Gannt Chart.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tunag\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PROJECTS\YMH212-Exponentia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BBDC575-28DD-4A39-9B7F-BAA38EED0844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B47228E5-F339-42A7-B66A-C446698638F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Görevler!$A$1:$X$40</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="295">
   <si>
     <t>Exponentia — 14 Haftalık Geliştirme + Bugfix Yol Haritası</t>
   </si>
@@ -935,6 +934,9 @@
   </si>
   <si>
     <t>Yağız</t>
+  </si>
+  <si>
+    <t>20/04/2026</t>
   </si>
 </sst>
 </file>
@@ -986,7 +988,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1060,6 +1062,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E0B4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1088,7 +1096,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1176,6 +1184,25 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1187,22 +1214,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFC6E0B4"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1619,16 +1641,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="H2" s="1" t="s">
@@ -1676,12 +1698,12 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A9" s="39" t="s">
+      <c r="A9" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
@@ -1754,13 +1776,13 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A17" s="37" t="s">
+      <c r="A17" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
+      <c r="B17" s="45"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
@@ -1856,14 +1878,14 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="38"/>
-      <c r="C26" s="38"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
@@ -1938,7 +1960,7 @@
       <c r="D30" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E30" s="44" t="s">
+      <c r="E30" s="38" t="s">
         <v>287</v>
       </c>
       <c r="F30" s="6" t="s">
@@ -1958,8 +1980,8 @@
       <c r="D31" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E31" s="11" t="s">
-        <v>54</v>
+      <c r="E31" s="38" t="s">
+        <v>287</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>58</v>
@@ -1978,8 +2000,8 @@
       <c r="D32" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E32" s="11" t="s">
-        <v>54</v>
+      <c r="E32" s="38" t="s">
+        <v>287</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>61</v>
@@ -2879,21 +2901,19 @@
         <v>0.25</v>
       </c>
       <c r="O9" s="16">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="P9" s="16">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="Q9" s="16">
-        <v>0.45</v>
-      </c>
-      <c r="R9" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="S9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="T9" s="44" t="s">
+        <v>0.25</v>
+      </c>
+      <c r="R9" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="S9" s="6"/>
+      <c r="T9" s="38" t="s">
         <v>287</v>
       </c>
       <c r="U9" s="18">
@@ -2902,15 +2922,15 @@
       </c>
       <c r="V9" s="18">
         <f t="shared" si="3"/>
-        <v>1.05</v>
+        <v>1.75</v>
       </c>
       <c r="W9" s="18">
         <f t="shared" si="4"/>
-        <v>1.05</v>
+        <v>1.75</v>
       </c>
       <c r="X9" s="18">
         <f t="shared" si="5"/>
-        <v>3.15</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.35">
@@ -2973,8 +2993,8 @@
       <c r="S10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="T10" s="44" t="s">
-        <v>287</v>
+      <c r="T10" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="U10" s="18">
         <f t="shared" si="2"/>
@@ -3053,7 +3073,7 @@
       <c r="S11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="T11" s="44" t="s">
+      <c r="T11" s="38" t="s">
         <v>287</v>
       </c>
       <c r="U11" s="18">
@@ -3133,7 +3153,7 @@
       <c r="S12" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="T12" s="44" t="s">
+      <c r="T12" s="38" t="s">
         <v>287</v>
       </c>
       <c r="U12" s="18">
@@ -3213,8 +3233,8 @@
       <c r="S13" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="T13" s="11" t="s">
-        <v>54</v>
+      <c r="T13" s="38" t="s">
+        <v>287</v>
       </c>
       <c r="U13" s="18">
         <f t="shared" si="2"/>
@@ -3293,8 +3313,8 @@
       <c r="S14" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="T14" s="11" t="s">
-        <v>54</v>
+      <c r="T14" s="38" t="s">
+        <v>287</v>
       </c>
       <c r="U14" s="18">
         <f t="shared" si="2"/>
@@ -3373,8 +3393,8 @@
       <c r="S15" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="T15" s="11" t="s">
-        <v>54</v>
+      <c r="T15" s="38" t="s">
+        <v>287</v>
       </c>
       <c r="U15" s="18">
         <f t="shared" si="2"/>
@@ -3453,8 +3473,8 @@
       <c r="S16" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="T16" s="11" t="s">
-        <v>54</v>
+      <c r="T16" s="38" t="s">
+        <v>287</v>
       </c>
       <c r="U16" s="18">
         <f t="shared" si="2"/>
@@ -3533,8 +3553,8 @@
       <c r="S17" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="T17" s="11" t="s">
-        <v>54</v>
+      <c r="T17" s="38" t="s">
+        <v>287</v>
       </c>
       <c r="U17" s="18">
         <f t="shared" si="2"/>
@@ -3613,8 +3633,8 @@
       <c r="S18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="T18" s="11" t="s">
-        <v>54</v>
+      <c r="T18" s="38" t="s">
+        <v>287</v>
       </c>
       <c r="U18" s="18">
         <f t="shared" si="2"/>
@@ -5342,15 +5362,15 @@
       </c>
       <c r="V40" s="8">
         <f>SUM(V2:V39)</f>
-        <v>63.449999999999989</v>
+        <v>64.149999999999991</v>
       </c>
       <c r="W40" s="8">
         <f>SUM(W2:W39)</f>
-        <v>64</v>
+        <v>64.700000000000017</v>
       </c>
       <c r="X40" s="8">
         <f>SUM(X2:X39)</f>
-        <v>64.850000000000009</v>
+        <v>63.45</v>
       </c>
     </row>
   </sheetData>
@@ -5373,30 +5393,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="48" t="s">
         <v>267</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
-      <c r="R1" s="38"/>
-      <c r="S1" s="38"/>
-      <c r="T1" s="38"/>
-      <c r="U1" s="38"/>
-      <c r="V1" s="38"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="45"/>
+      <c r="Q1" s="45"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="45"/>
+      <c r="T1" s="45"/>
+      <c r="U1" s="45"/>
+      <c r="V1" s="45"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
@@ -5411,7 +5431,7 @@
       <c r="D3" s="25" t="s">
         <v>270</v>
       </c>
-      <c r="E3" s="45" t="s">
+      <c r="E3" s="39" t="s">
         <v>288</v>
       </c>
     </row>
@@ -5972,17 +5992,17 @@
       <c r="D13" s="27">
         <v>7</v>
       </c>
-      <c r="E13" s="44" t="s">
+      <c r="E13" s="38" t="s">
         <v>287</v>
       </c>
-      <c r="F13" s="43" t="s">
+      <c r="F13" s="37" t="s">
         <v>285</v>
       </c>
       <c r="G13" s="36">
         <v>46090</v>
       </c>
-      <c r="H13" s="36">
-        <v>46104</v>
+      <c r="H13" s="40" t="s">
+        <v>294</v>
       </c>
       <c r="I13" s="31" t="s">
         <v>138</v>
@@ -5996,17 +6016,17 @@
       <c r="L13" s="42" t="s">
         <v>286</v>
       </c>
-      <c r="M13" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="N13" s="30" t="s">
-        <v>138</v>
-      </c>
-      <c r="O13" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="P13" s="30" t="s">
-        <v>138</v>
+      <c r="M13" s="42" t="s">
+        <v>286</v>
+      </c>
+      <c r="N13" s="42" t="s">
+        <v>286</v>
+      </c>
+      <c r="O13" s="42" t="s">
+        <v>286</v>
+      </c>
+      <c r="P13" s="42" t="s">
+        <v>286</v>
       </c>
       <c r="Q13" s="31" t="s">
         <v>138</v>
@@ -6040,8 +6060,8 @@
       <c r="D14" s="27">
         <v>8</v>
       </c>
-      <c r="E14" s="44" t="s">
-        <v>287</v>
+      <c r="E14" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="F14" s="28" t="s">
         <v>17</v>
@@ -6058,10 +6078,10 @@
       <c r="J14" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="K14" s="33" t="s">
+      <c r="K14" s="41" t="s">
         <v>289</v>
       </c>
-      <c r="L14" s="33" t="s">
+      <c r="L14" s="41" t="s">
         <v>289</v>
       </c>
       <c r="M14" s="31" t="s">
@@ -6108,7 +6128,7 @@
       <c r="D15" s="27">
         <v>8</v>
       </c>
-      <c r="E15" s="44" t="s">
+      <c r="E15" s="38" t="s">
         <v>287</v>
       </c>
       <c r="F15" s="12" t="s">
@@ -6126,10 +6146,10 @@
       <c r="J15" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="K15" s="33" t="s">
+      <c r="K15" s="42" t="s">
         <v>290</v>
       </c>
-      <c r="L15" s="33" t="s">
+      <c r="L15" s="42" t="s">
         <v>290</v>
       </c>
       <c r="M15" s="31" t="s">
@@ -6176,7 +6196,7 @@
       <c r="D16" s="27">
         <v>4</v>
       </c>
-      <c r="E16" s="44" t="s">
+      <c r="E16" s="38" t="s">
         <v>287</v>
       </c>
       <c r="F16" s="32" t="s">
@@ -6194,7 +6214,7 @@
       <c r="J16" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="K16" s="33" t="s">
+      <c r="K16" s="42" t="s">
         <v>293</v>
       </c>
       <c r="L16" s="30" t="s">
@@ -6244,8 +6264,8 @@
       <c r="D17" s="27">
         <v>8</v>
       </c>
-      <c r="E17" s="11" t="s">
-        <v>54</v>
+      <c r="E17" s="38" t="s">
+        <v>287</v>
       </c>
       <c r="F17" s="34" t="s">
         <v>21</v>
@@ -6265,10 +6285,10 @@
       <c r="K17" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="L17" s="33" t="s">
+      <c r="L17" s="42" t="s">
         <v>291</v>
       </c>
-      <c r="M17" s="33" t="s">
+      <c r="M17" s="42" t="s">
         <v>291</v>
       </c>
       <c r="N17" s="30" t="s">
@@ -6312,8 +6332,8 @@
       <c r="D18" s="27">
         <v>7</v>
       </c>
-      <c r="E18" s="11" t="s">
-        <v>54</v>
+      <c r="E18" s="38" t="s">
+        <v>287</v>
       </c>
       <c r="F18" s="12" t="s">
         <v>25</v>
@@ -6333,10 +6353,10 @@
       <c r="K18" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="L18" s="33" t="s">
+      <c r="L18" s="42" t="s">
         <v>290</v>
       </c>
-      <c r="M18" s="33" t="s">
+      <c r="M18" s="42" t="s">
         <v>290</v>
       </c>
       <c r="N18" s="30" t="s">
@@ -6380,8 +6400,8 @@
       <c r="D19" s="27">
         <v>6</v>
       </c>
-      <c r="E19" s="11" t="s">
-        <v>54</v>
+      <c r="E19" s="38" t="s">
+        <v>287</v>
       </c>
       <c r="F19" s="34" t="s">
         <v>21</v>
@@ -6401,10 +6421,10 @@
       <c r="K19" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="L19" s="33" t="s">
+      <c r="L19" s="42" t="s">
         <v>291</v>
       </c>
-      <c r="M19" s="33" t="s">
+      <c r="M19" s="42" t="s">
         <v>291</v>
       </c>
       <c r="N19" s="30" t="s">
@@ -6448,8 +6468,8 @@
       <c r="D20" s="27">
         <v>7</v>
       </c>
-      <c r="E20" s="11" t="s">
-        <v>54</v>
+      <c r="E20" s="38" t="s">
+        <v>287</v>
       </c>
       <c r="F20" s="28" t="s">
         <v>17</v>
@@ -6472,10 +6492,10 @@
       <c r="L20" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="M20" s="33" t="s">
+      <c r="M20" s="42" t="s">
         <v>289</v>
       </c>
-      <c r="N20" s="33" t="s">
+      <c r="N20" s="42" t="s">
         <v>289</v>
       </c>
       <c r="O20" s="31" t="s">
@@ -6516,8 +6536,8 @@
       <c r="D21" s="27">
         <v>7</v>
       </c>
-      <c r="E21" s="11" t="s">
-        <v>54</v>
+      <c r="E21" s="38" t="s">
+        <v>287</v>
       </c>
       <c r="F21" s="32" t="s">
         <v>29</v>
@@ -6540,13 +6560,13 @@
       <c r="L21" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="M21" s="33" t="s">
+      <c r="M21" s="42" t="s">
         <v>293</v>
       </c>
-      <c r="N21" s="33" t="s">
+      <c r="N21" s="42" t="s">
         <v>293</v>
       </c>
-      <c r="O21" s="33" t="s">
+      <c r="O21" s="42" t="s">
         <v>293</v>
       </c>
       <c r="P21" s="30" t="s">
@@ -6584,8 +6604,8 @@
       <c r="D22" s="27">
         <v>7</v>
       </c>
-      <c r="E22" s="11" t="s">
-        <v>54</v>
+      <c r="E22" s="38" t="s">
+        <v>287</v>
       </c>
       <c r="F22" s="34" t="s">
         <v>21</v>
@@ -6608,10 +6628,10 @@
       <c r="L22" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="M22" s="33" t="s">
+      <c r="M22" s="42" t="s">
         <v>291</v>
       </c>
-      <c r="N22" s="33" t="s">
+      <c r="N22" s="42" t="s">
         <v>291</v>
       </c>
       <c r="O22" s="31" t="s">
@@ -6679,10 +6699,10 @@
       <c r="M23" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="N23" s="33" t="s">
+      <c r="N23" s="42" t="s">
         <v>289</v>
       </c>
-      <c r="O23" s="33" t="s">
+      <c r="O23" s="42" t="s">
         <v>289</v>
       </c>
       <c r="P23" s="30" t="s">
@@ -8072,5 +8092,6 @@
     <mergeCell ref="A1:V1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>